--- a/output/club_history_dospeli.xlsx
+++ b/output/club_history_dospeli.xlsx
@@ -1378,31 +1378,31 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="n">
         <v>39</v>
       </c>
-      <c r="E16" t="n">
-        <v>38</v>
-      </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
         <v>16</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>0.4102564102564102</v>
       </c>
-      <c r="J16" s="2" t="n">
-        <v>0.3947368421052632</v>
-      </c>
       <c r="K16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L16" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="M16" t="n">
         <v>10</v>
@@ -1411,10 +1411,10 @@
         <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
         <v>2.4</v>
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -1883,13 +1883,13 @@
         <v>1.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
         <v>9</v>
       </c>
-      <c r="E29" t="n">
-        <v>8</v>
-      </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
         <v>3</v>
@@ -2160,10 +2160,10 @@
         <v>3</v>
       </c>
       <c r="I29" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>0.375</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B, D</t>
+          <t>B, C, D</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G30" t="n">
         <v>3</v>
@@ -2219,10 +2219,10 @@
         <v>4</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="K30" t="n">
         <v>7</v>
@@ -2499,46 +2499,46 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
         <v>9</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="K35" t="n">
         <v>8</v>
       </c>
-      <c r="F35" t="n">
-        <v>17</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="L35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P35" t="n">
         <v>4</v>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3</v>
-      </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="36">
@@ -2967,31 +2967,31 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
@@ -3000,13 +3000,13 @@
         <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -3870,11 +3870,11 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Roušar Petr</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -3965,11 +3965,11 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Břicháček Bedřich</t>
+          <t>Roušar Petr</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Břicháček Bedřich</t>
+          <t>Bubeník Jan</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -4060,11 +4060,11 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Suvorov Maksym</t>
+          <t>Břicháček Bedřich</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Bubeník Jan</t>
+          <t>Břicháček Bedřich</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4155,11 +4155,11 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Volf Jakub</t>
+          <t>Suvorov Maksym</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -4250,11 +4250,11 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Uhlířová Veronika</t>
+          <t>Volf Jakub</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>3.33</v>
+        <v>3.56</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Kubín Marian</t>
+          <t>Uhlířová Veronika</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Kubín Marian</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -4582,11 +4582,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Břicháček Bedřich</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -4638,11 +4638,11 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Kubín Marian</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4677,11 +4677,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Přibyl Tadeáš</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Kubín Marian</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Břicháček Bedřich</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tichý Tomáš</t>
+          <t>Přibyl Tadeáš</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Špejzlová Martina</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -4915,11 +4915,11 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Přibyl Tadeáš</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Tichý Tomáš</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -4994,11 +4994,11 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Přibyl Tadeáš</t>
+          <t>Špejzlová Martina</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5033,11 +5033,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jech Martin</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Přibyl Tadeáš</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Pikula Tomáš</t>
+          <t>Přibyl Tadeáš</t>
         </is>
       </c>
       <c r="U20" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Jech Martin</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5136,15 +5136,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Laňarová Kateřina</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
@@ -5152,15 +5152,15 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nováčková Karolína</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.5423728813559322</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Königsmark Jan</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Pikula Tomáš</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Kotlasová Klára</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -5239,31 +5239,31 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laňarová Kateřina</t>
+          <t>Kotlasová Klára</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tichá Lenka</t>
+          <t>Nováčková Karolína</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Jech Martin</t>
+          <t>Königsmark Jan</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Tichý Tomáš</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -5334,15 +5334,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Bubeník Jan</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bušková Michaela</t>
+          <t>Tichá Lenka</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -5350,15 +5350,15 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Jech Martin</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Kotlasová Klára</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -5374,11 +5374,11 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jech Martin</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -5398,11 +5398,11 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Jech Martin</t>
+          <t>Tichý Tomáš</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="24">
@@ -5429,15 +5429,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bubeník Jan</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Bušková Michaela</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Jech Martin</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Přibyl Tadeáš</t>
+          <t>Jech Martin</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5524,11 +5524,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Kubín Marian</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Čambor Radovan</t>
+          <t>Kotlasová Klára</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -5584,15 +5584,15 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Bubeník Jan</t>
+          <t>Přibyl Tadeáš</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="26">
@@ -5619,27 +5619,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Bušková Michaela</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Skopcová Valerie</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Bělov Petr</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bělov Petr</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Přibyl Tadeáš</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hýbl Jan ml.</t>
+          <t>Čambor Radovan</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -5683,11 +5683,11 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5714,27 +5714,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kubín Marian</t>
+          <t>Bělov Petr</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Skopcová Valerie</t>
+          <t>Bubeník Jan</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Laňarová Kateřina</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pikula Tomáš</t>
+          <t>Hýbl Jan ml.</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -5778,11 +5778,11 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Bubeník Jan</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Laňarová Kateřina</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bušková Michaela</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
@@ -5825,11 +5825,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Bělov Petr</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Königsmark Jan</t>
+          <t>Pikula Tomáš</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Čambor Radovan</t>
+          <t>Kotlasová Klára</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tichý Tomáš</t>
+          <t>Laňarová Kateřina</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tichý Tomáš</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mlejnek Roman</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -5920,11 +5920,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Mlejnek Roman</t>
+          <t>Přibyl Tadeáš</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -5936,15 +5936,15 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>Boutineau Lenka</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>Königsmark Jan</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Bělov Petr</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Schwarz Ondřej</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Čambor Radovan</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="30">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Königsmark Jan</t>
+          <t>Tichý Tomáš</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5991,31 +5991,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Königsmark Jan</t>
+          <t>Tichý Tomáš</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Vydlák Šimon</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bubeník Jan</t>
+          <t>Bělov Petr</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Laňarová Kateřina</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -6031,15 +6031,15 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t>Königsmark Jan</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
           <t>Bělov Petr</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -6047,11 +6047,11 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Doležel Jiří</t>
+          <t>Schwarz Ondřej</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6063,11 +6063,11 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Hýbl Jan ml.</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="31">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bělov Petr</t>
+          <t>Königsmark Jan</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bělov Petr</t>
+          <t>Königsmark Jan</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -6094,11 +6094,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vydlák Šimon</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mlejnek Roman</t>
+          <t>Bělov Petr</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -6134,15 +6134,15 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Laňarová Kateřina</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Hýbl Jan ml.</t>
+          <t>Doležel Jiří</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Schwarz Ondřej</t>
+          <t>Hýbl Jan ml.</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -6173,75 +6173,75 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Bělov Petr</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bělov Petr</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Mlejnek Roman</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="G32" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kotlasová Klára</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Klusáková Lucie</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>12</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Pikula Tomáš</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Mlejnek Roman</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Königsmark Jan</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Mlejnek Roman</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Laňarová Kateřina</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>Hýbl Jan ml.</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>11</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Pikula Tomáš</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Klusáková Lucka</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>3</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Tichý Tomáš</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Bušková Michaela</t>
-        </is>
-      </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Schwarz Ondřej</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -6284,15 +6284,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Königsmark Jan</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kotlasová Klára</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
@@ -6300,11 +6300,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Pikula Tomáš</t>
+          <t>Hýbl Jan ml.</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Schwarz Ondřej</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mlejnek Roman</t>
+          <t>Tichý Tomáš</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Bělov Petr</t>
+          <t>Bušková Michaela</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -6371,11 +6371,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Schwarz Ondřej</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Pikula Tomáš</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Tichý Tomáš</t>
+          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -6411,15 +6411,15 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Špejzlová Martina</t>
+          <t>Schwarz Ondřej</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Klusáková Lucka</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mlejnek Roman</t>
+          <t>Bělov Petr</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -6458,15 +6458,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Klusáková Lucie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Schwarz Ondřej</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Boutineau Lenka</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -6498,31 +6498,31 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Tichý Tomáš</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Špejzlová Martina</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>Klusáková Lucka</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Boutineau Lenka</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Olšák Petr</t>
-        </is>
-      </c>
       <c r="Q35" t="n">
         <v>3</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Mlejnek Roman</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Schwarz Ondřej</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -6561,11 +6561,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Schwarz Ondřej</t>
+          <t>Klusáková Lucka</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -6601,15 +6601,15 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t>Klusáková Lucie</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
           <t>Olšák Petr</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>2</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Boutineau Lenka</t>
+          <t>Schwarz Ondřej</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Olšák Petr</t>
+          <t>Klusáková Lucie</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Klusáková Lucie</t>
+          <t>Olšák Petr</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -8342,19 +8342,19 @@
         <v>19.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
@@ -8703,19 +8703,19 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -8920,10 +8920,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B, D</t>
+          <t>B, C, D</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -8967,10 +8967,10 @@
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
@@ -9175,19 +9175,19 @@
         <v>0.5</v>
       </c>
       <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="J35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -9448,19 +9448,19 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
         <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
